--- a/data/formations-suivi-inscriptions.xlsx
+++ b/data/formations-suivi-inscriptions.xlsx
@@ -33,40 +33,40 @@
     <t>n_registration</t>
   </si>
   <si>
-    <t>Reproducibility</t>
+    <t xml:space="preserve">Intelligence artificielle</t>
+  </si>
+  <si>
+    <t>artificial-intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donnée de biodiversité</t>
+  </si>
+  <si>
+    <t>biodiversity-data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revue systématique</t>
+  </si>
+  <si>
+    <t>literature-synthesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réseaux d'interaction</t>
+  </si>
+  <si>
+    <t>network-analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche reproductible</t>
   </si>
   <si>
     <t>reproducibility</t>
   </si>
   <si>
-    <t xml:space="preserve">Theoretical models</t>
+    <t xml:space="preserve">Modélisation théorique</t>
   </si>
   <si>
     <t>theoretical-models</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Literature synthesis</t>
-  </si>
-  <si>
-    <t>literature-synthesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network analysis</t>
-  </si>
-  <si>
-    <t>network-analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biodiversity data</t>
-  </si>
-  <si>
-    <t>biodiversity-data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artificial intelligence</t>
-  </si>
-  <si>
-    <t>artificial-intelligence</t>
   </si>
 </sst>
 </file>
@@ -698,13 +698,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D2" s="7">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E2" s="3">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="16.5">
@@ -715,268 +715,268 @@
         <v>6</v>
       </c>
       <c r="C3" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="D3" s="7">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E3" s="3">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="16.5">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D4" s="7">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E4" s="3">
-        <v>94</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="16.5">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D5" s="7">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E5" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="16.5">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D6" s="7">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E6" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="16.5">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D7" s="7">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E7" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="16.5">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D8" s="7">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E8" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="16.5">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D9" s="7">
         <v>150</v>
       </c>
       <c r="E9" s="3">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" ht="16.5">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D10" s="7">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E10" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="16.5">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D11" s="7">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="16.5">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D12" s="7">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E12" s="3">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" ht="16.5">
       <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="C13" s="2">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D13" s="7">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E13" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="16.5">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
       </c>
       <c r="E14" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="16.5">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="D15" s="7">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E15" s="3">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" ht="16.5">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="D16" s="7">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" ht="16.5">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D17" s="7">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E17" s="3">
-        <v>46</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" ht="16.5">
       <c r="A18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C18" s="2">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D18" s="7">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" ht="16.5">
@@ -987,13 +987,13 @@
         <v>14</v>
       </c>
       <c r="C19" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D19" s="7">
         <v>150</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" ht="16.5">
@@ -1004,21 +1004,21 @@
         <v>14</v>
       </c>
       <c r="C20" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D20" s="7">
         <v>250</v>
       </c>
       <c r="E20" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" ht="16.5">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C21" s="2">
         <v>2025</v>
@@ -1027,15 +1027,15 @@
         <v>250</v>
       </c>
       <c r="E21" s="3">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="16.5">
       <c r="A22" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C22" s="2">
         <v>2026</v>
@@ -1044,44 +1044,99 @@
         <v>250</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="16.5">
       <c r="A23" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="D23" s="7">
         <v>150</v>
       </c>
       <c r="E23" s="3">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" ht="16.5">
       <c r="A24" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D24" s="7">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5">
+      <c r="A25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D25" s="7">
+        <v>150</v>
+      </c>
+      <c r="E25" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2025</v>
+      </c>
+      <c r="D26" s="7">
+        <v>250</v>
+      </c>
+      <c r="E26" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="2">
         <v>2026</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D27" s="7">
         <v>150</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E27" s="3">
         <v>25</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:E27" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="A2:A27"/>
+    <sortCondition sortBy="value" descending="0" ref="C2:C27"/>
+  </sortState>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
@@ -1370,7 +1425,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8899008-0902-487F-8AD9-96D6E33BEE3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="A8899008-0902-487F-8AD9-96D6E33BEE3A">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
@@ -1382,7 +1437,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95BF5E31-36B9-46D7-93FB-144A89CF3CE6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="95BF5E31-36B9-46D7-93FB-144A89CF3CE6">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -1390,7 +1445,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8AF860E-CB0A-4E25-8A80-03908EE4B437}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="D8AF860E-CB0A-4E25-8A80-03908EE4B437">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
